--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>3640000</v>
       </c>
       <c r="C2" t="n">
-        <v>1283074.2</v>
+        <v>1516384.92</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>410168.96</v>
+        <v>51748.9</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>3.4%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>872905.2399999999</v>
+        <v>1464636.02</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1120000</v>
       </c>
       <c r="C3" t="n">
-        <v>467449.36</v>
+        <v>534687.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>139000</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>328449.36</v>
+        <v>534687.36</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>2243289.59</v>
+        <v>3358536.8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>200826.65</v>
+        <v>1506</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2042462.94</v>
+        <v>3357030.8</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -467,19 +467,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>51748.9</v>
+        <v>489714.96</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3.4%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1464636.02</v>
+        <v>1026669.96</v>
       </c>
     </row>
     <row r="3">
@@ -496,19 +496,19 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>170300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>534687.36</v>
+        <v>364387.36</v>
       </c>
     </row>
     <row r="4">
@@ -525,19 +525,19 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1506</v>
+        <v>214021.65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3357030.8</v>
+        <v>3144515.15</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>3640000</v>
       </c>
       <c r="C2" t="n">
-        <v>1516384.92</v>
+        <v>1763322.91</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>489714.96</v>
+        <v>547458.96</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1026669.96</v>
+        <v>1215863.95</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1120000</v>
       </c>
       <c r="C3" t="n">
-        <v>534687.36</v>
+        <v>551647.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>170300</v>
+        <v>176900</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>364387.36</v>
+        <v>374747.36</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>3358536.8</v>
+        <v>3565083.01</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>38.2%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>214021.65</v>
+        <v>251478.65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3144515.15</v>
+        <v>3313604.359999999</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>3640000</v>
       </c>
       <c r="C2" t="n">
-        <v>1763322.91</v>
+        <v>1893777.9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>36.5%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>547458.96</v>
+        <v>565113.96</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1215863.95</v>
+        <v>1328663.94</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1120000</v>
       </c>
       <c r="C3" t="n">
-        <v>551647.36</v>
+        <v>598562.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>176900</v>
+        <v>215700</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>374747.36</v>
+        <v>382862.36</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>3565083.01</v>
+        <v>3653224.11</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>251478.65</v>
+        <v>320329.65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>8.8%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3313604.359999999</v>
+        <v>3332894.46</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>3640000</v>
       </c>
       <c r="C2" t="n">
-        <v>1893777.9</v>
+        <v>1984590.11</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>565113.96</v>
+        <v>666208.9600000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1328663.94</v>
+        <v>1318381.15</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1120000</v>
       </c>
       <c r="C3" t="n">
-        <v>598562.36</v>
+        <v>698349.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>215700</v>
+        <v>258700</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>382862.36</v>
+        <v>439649.36</v>
       </c>
     </row>
     <row r="4">
@@ -521,15 +521,15 @@
         <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>3653224.11</v>
+        <v>3942539.11</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>320329.65</v>
+        <v>347347.65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3332894.46</v>
+        <v>3595191.46</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -521,11 +521,11 @@
         <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>3942539.11</v>
+        <v>4026791.09</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -533,11 +533,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3595191.46</v>
+        <v>3679443.44</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>3640000</v>
       </c>
       <c r="C2" t="n">
-        <v>1984590.11</v>
+        <v>2260103.51</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>666208.9600000001</v>
+        <v>691405.76</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1318381.15</v>
+        <v>1568697.75</v>
       </c>
     </row>
     <row r="3">
@@ -492,11 +492,11 @@
         <v>1120000</v>
       </c>
       <c r="C3" t="n">
-        <v>698349.36</v>
+        <v>728727.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -504,11 +504,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>439649.36</v>
+        <v>470027.36</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>4026791.09</v>
+        <v>4221035.49</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>347347.65</v>
+        <v>393499.05</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3679443.44</v>
+        <v>3827536.44</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>3640000</v>
       </c>
       <c r="C2" t="n">
-        <v>2260103.51</v>
+        <v>2360845.31</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>691405.76</v>
+        <v>703153.76</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1568697.75</v>
+        <v>1657691.55</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1120000</v>
       </c>
       <c r="C3" t="n">
-        <v>728727.36</v>
+        <v>824467.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>258700</v>
+        <v>286700</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>470027.36</v>
+        <v>537767.36</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>4221035.49</v>
+        <v>4933201.79</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>393499.05</v>
+        <v>420003.05</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3827536.44</v>
+        <v>4513198.74</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>3640000</v>
       </c>
       <c r="C2" t="n">
-        <v>2360845.31</v>
+        <v>2330718.31</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>703153.76</v>
+        <v>723759.76</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1657691.55</v>
+        <v>1606958.55</v>
       </c>
     </row>
     <row r="3">
@@ -492,11 +492,11 @@
         <v>1120000</v>
       </c>
       <c r="C3" t="n">
-        <v>824467.36</v>
+        <v>833538.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -504,11 +504,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>537767.36</v>
+        <v>546838.36</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>4933201.79</v>
+        <v>5049253.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>420003.05</v>
+        <v>419983.05</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4513198.74</v>
+        <v>4629270.35</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,11 +463,11 @@
         <v>3640000</v>
       </c>
       <c r="C2" t="n">
-        <v>2330718.31</v>
+        <v>2418881.31</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -475,11 +475,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>29.9%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1606958.55</v>
+        <v>1695121.55</v>
       </c>
     </row>
     <row r="3">
@@ -492,11 +492,11 @@
         <v>1120000</v>
       </c>
       <c r="C3" t="n">
-        <v>833538.36</v>
+        <v>864067.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -504,11 +504,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>546838.36</v>
+        <v>577367.36</v>
       </c>
     </row>
     <row r="4">
@@ -521,11 +521,11 @@
         <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>5049253.4</v>
+        <v>5197161.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -533,11 +533,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4629270.35</v>
+        <v>4777178.35</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,7 +463,7 @@
         <v>3640000</v>
       </c>
       <c r="C2" t="n">
-        <v>2418881.31</v>
+        <v>2419679.31</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1695121.55</v>
+        <v>1695919.55</v>
       </c>
     </row>
     <row r="3">
@@ -492,11 +492,11 @@
         <v>1120000</v>
       </c>
       <c r="C3" t="n">
-        <v>864067.36</v>
+        <v>838247.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -504,11 +504,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>577367.36</v>
+        <v>551547.36</v>
       </c>
     </row>
     <row r="4">
@@ -521,7 +521,7 @@
         <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>5197161.4</v>
+        <v>5201170.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4777178.35</v>
+        <v>4781187.35</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,7 +463,7 @@
         <v>3640000</v>
       </c>
       <c r="C2" t="n">
-        <v>2419679.31</v>
+        <v>2418881.31</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -479,7 +479,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1695919.55</v>
+        <v>1695121.55</v>
       </c>
     </row>
     <row r="3">
@@ -492,11 +492,11 @@
         <v>1120000</v>
       </c>
       <c r="C3" t="n">
-        <v>838247.36</v>
+        <v>864067.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -504,11 +504,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>33.2%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>551547.36</v>
+        <v>577367.36</v>
       </c>
     </row>
     <row r="4">
@@ -521,7 +521,7 @@
         <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>5201170.4</v>
+        <v>5197161.4</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4781187.35</v>
+        <v>4777178.35</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>3640000</v>
       </c>
       <c r="C2" t="n">
-        <v>2418881.31</v>
+        <v>2711772.64</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>723759.76</v>
+        <v>788885.76</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1695121.55</v>
+        <v>1922886.88</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1120000</v>
       </c>
       <c r="C3" t="n">
-        <v>864067.36</v>
+        <v>863847.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>286700</v>
+        <v>295700</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>577367.36</v>
+        <v>568147.36</v>
       </c>
     </row>
     <row r="4">
@@ -521,15 +521,15 @@
         <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>5197161.4</v>
+        <v>5373732.240000001</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>419983.05</v>
+        <v>433021.05</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -537,7 +537,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4777178.35</v>
+        <v>4940711.19</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>3640000</v>
       </c>
       <c r="C2" t="n">
-        <v>2711772.64</v>
+        <v>2803134.96</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>788885.76</v>
+        <v>825961.76</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1922886.88</v>
+        <v>1977173.2</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1120000</v>
       </c>
       <c r="C3" t="n">
-        <v>863847.36</v>
+        <v>843371.8300000001</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>295700</v>
+        <v>315500</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>568147.36</v>
+        <v>527871.8300000001</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>5373732.240000001</v>
+        <v>5613264.380000001</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>433021.05</v>
+        <v>435120.05</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4940711.19</v>
+        <v>5178144.330000001</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>3640000</v>
       </c>
       <c r="C2" t="n">
-        <v>2803134.96</v>
+        <v>1893777.9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>825961.76</v>
+        <v>0</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1977173.2</v>
+        <v>1893777.9</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1120000</v>
       </c>
       <c r="C3" t="n">
-        <v>843371.8300000001</v>
+        <v>910887.8300000001</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>315500</v>
+        <v>377900</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>527871.8300000001</v>
+        <v>532987.8300000001</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>5613264.380000001</v>
+        <v>5771537.390000001</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>435120.05</v>
+        <v>521677.05</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5178144.330000001</v>
+        <v>5249860.340000001</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>3640000</v>
       </c>
       <c r="C2" t="n">
-        <v>1893777.9</v>
+        <v>2852339.9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>623555.16</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1893777.9</v>
+        <v>2228784.74</v>
       </c>
     </row>
     <row r="3">

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>3640000</v>
       </c>
       <c r="C2" t="n">
-        <v>2852339.9</v>
+        <v>3039467.9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>623555.16</v>
+        <v>629255.16</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>20.7%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2228784.74</v>
+        <v>2410212.74</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1120000</v>
       </c>
       <c r="C3" t="n">
-        <v>910887.8300000001</v>
+        <v>927927.8300000001</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>48.2%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>377900</v>
+        <v>388060</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>532987.8300000001</v>
+        <v>539867.8300000001</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>5771537.390000001</v>
+        <v>6296953.37</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>521677.05</v>
+        <v>618796.42</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5249860.340000001</v>
+        <v>5678156.95</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -467,19 +467,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>629255.16</v>
+        <v>637385.16</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.7%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2410212.74</v>
+        <v>2402082.74</v>
       </c>
     </row>
     <row r="3">

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,11 +463,11 @@
         <v>3640000</v>
       </c>
       <c r="C2" t="n">
-        <v>3039467.9</v>
+        <v>3060085.9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -475,11 +475,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2402082.74</v>
+        <v>2422700.74</v>
       </c>
     </row>
     <row r="3">
@@ -492,11 +492,11 @@
         <v>1120000</v>
       </c>
       <c r="C3" t="n">
-        <v>927927.8300000001</v>
+        <v>934527.8300000001</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>48.2%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -504,11 +504,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>539867.8300000001</v>
+        <v>546467.8300000001</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>6296953.37</v>
+        <v>6562784.13</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>618796.42</v>
+        <v>618815.42</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5678156.95</v>
+        <v>5943968.71</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>3640000</v>
       </c>
       <c r="C2" t="n">
-        <v>3060085.9</v>
+        <v>3258742.9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>637385.16</v>
+        <v>704245.5600000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2422700.74</v>
+        <v>2554497.34</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1120000</v>
       </c>
       <c r="C3" t="n">
-        <v>934527.8300000001</v>
+        <v>1007327.83</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>388060</v>
+        <v>419460</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>546467.8300000001</v>
+        <v>587867.83</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>6562784.13</v>
+        <v>6790943.57</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>618815.42</v>
+        <v>723513.66</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5943968.71</v>
+        <v>6067429.910000001</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -467,19 +467,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>704245.5600000001</v>
+        <v>707245.5600000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21.6%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2554497.34</v>
+        <v>2551497.34</v>
       </c>
     </row>
     <row r="3">

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>3640000</v>
       </c>
       <c r="C2" t="n">
-        <v>3258742.9</v>
+        <v>3289002.9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>707245.5600000001</v>
+        <v>639763.5600000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21.7%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2551497.34</v>
+        <v>2649239.34</v>
       </c>
     </row>
     <row r="3">
@@ -492,11 +492,11 @@
         <v>1120000</v>
       </c>
       <c r="C3" t="n">
-        <v>1007327.83</v>
+        <v>1034247.83</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -504,11 +504,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>587867.83</v>
+        <v>614787.83</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>6790943.57</v>
+        <v>6993378.080000001</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>723513.66</v>
+        <v>752494.66</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>6067429.910000001</v>
+        <v>6240883.42</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>3640000</v>
       </c>
       <c r="C2" t="n">
-        <v>3289002.9</v>
+        <v>3498323.9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>639763.5600000001</v>
+        <v>674523.5600000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>19.3%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2649239.34</v>
+        <v>2823800.34</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1120000</v>
       </c>
       <c r="C3" t="n">
-        <v>1034247.83</v>
+        <v>1235647.83</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>419460</v>
+        <v>444276</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>614787.83</v>
+        <v>791371.8300000001</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>8240000</v>
       </c>
       <c r="C4" t="n">
-        <v>6993378.080000001</v>
+        <v>7167467.690000001</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>77.2%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>752494.66</v>
+        <v>809351.66</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>6240883.42</v>
+        <v>6358116.03</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,84 +460,55 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3640000</v>
+        <v>5850000</v>
       </c>
       <c r="C2" t="n">
-        <v>3498323.9</v>
+        <v>245429.23</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>674523.5600000001</v>
+        <v>48960</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19.3%</t>
+          <t>19.9%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2823800.34</v>
+        <v>196469.23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>班主任</t>
+          <t>门店</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1120000</v>
+        <v>8240000</v>
       </c>
       <c r="C3" t="n">
-        <v>1235647.83</v>
+        <v>704667.03</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>444276</v>
+        <v>66</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>791371.8300000001</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>门店</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>8240000</v>
-      </c>
-      <c r="C4" t="n">
-        <v>7167467.690000001</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>77.2%</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>809351.66</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>11.3%</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>6358116.03</v>
+        <v>704601.03</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>5850000</v>
       </c>
       <c r="C2" t="n">
-        <v>245429.23</v>
+        <v>446986.22</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>48960</v>
+        <v>151803</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19.9%</t>
+          <t>34.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>196469.23</v>
+        <v>295183.22</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>8240000</v>
       </c>
       <c r="C3" t="n">
-        <v>704667.03</v>
+        <v>884758.8499999999</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>9.3%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>66</v>
+        <v>118846</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>704601.03</v>
+        <v>765912.8499999999</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>5850000</v>
       </c>
       <c r="C2" t="n">
-        <v>446986.22</v>
+        <v>687789.12</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>151803</v>
+        <v>199853.04</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>34.0%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>295183.22</v>
+        <v>487936.08</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>8240000</v>
       </c>
       <c r="C3" t="n">
-        <v>884758.8499999999</v>
+        <v>1104028.16</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>118846</v>
+        <v>144374</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>765912.8499999999</v>
+        <v>959654.1599999998</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>5850000</v>
       </c>
       <c r="C2" t="n">
-        <v>687789.12</v>
+        <v>893338.0599999999</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>199853.04</v>
+        <v>291192.04</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>487936.08</v>
+        <v>602146.02</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>8240000</v>
       </c>
       <c r="C3" t="n">
-        <v>1104028.16</v>
+        <v>2070801.84</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>144374</v>
+        <v>228382.33</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>959654.1599999998</v>
+        <v>1842419.51</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -460,14 +460,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5850000</v>
+        <v>5900000</v>
       </c>
       <c r="C2" t="n">
         <v>893338.0599999999</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.1%</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -489,14 +489,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8240000</v>
+        <v>9370000</v>
       </c>
       <c r="C3" t="n">
         <v>2070801.84</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>19.7%</t>
         </is>
       </c>
       <c r="E3" t="n">

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -489,14 +489,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9370000</v>
+        <v>11300000</v>
       </c>
       <c r="C3" t="n">
         <v>2070801.84</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="E3" t="n">

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -489,14 +489,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11300000</v>
+        <v>12600000</v>
       </c>
       <c r="C3" t="n">
         <v>2070801.84</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="E3" t="n">

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>5900000</v>
       </c>
       <c r="C2" t="n">
-        <v>893338.0599999999</v>
+        <v>1064294.06</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>15.1%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>291192.04</v>
+        <v>381953.79</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>602146.02</v>
+        <v>682340.27</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>12600000</v>
       </c>
       <c r="C3" t="n">
-        <v>2070801.84</v>
+        <v>2274653.87</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228382.33</v>
+        <v>271798.33</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1842419.51</v>
+        <v>2002855.54</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,11 +463,11 @@
         <v>5900000</v>
       </c>
       <c r="C2" t="n">
-        <v>1064294.06</v>
+        <v>682340.27</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -489,14 +489,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12600000</v>
+        <v>9370000</v>
       </c>
       <c r="C3" t="n">
-        <v>2274653.87</v>
+        <v>2002855.54</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="E3" t="n">

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -489,14 +489,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9370000</v>
+        <v>12600000</v>
       </c>
       <c r="C3" t="n">
         <v>2002855.54</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="E3" t="n">

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,11 +463,11 @@
         <v>5900000</v>
       </c>
       <c r="C2" t="n">
-        <v>682340.27</v>
+        <v>1064294.06</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -489,14 +489,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12600000</v>
+        <v>11300000</v>
       </c>
       <c r="C3" t="n">
-        <v>2002855.54</v>
+        <v>2274653.87</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="E3" t="n">

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,58 +456,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>销售</t>
+          <t>一阶</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5900000</v>
+        <v>4300000</v>
       </c>
       <c r="C2" t="n">
-        <v>1064294.06</v>
+        <v>705390.7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>16.4%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>381953.79</v>
+        <v>229289.79</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>682340.27</v>
+        <v>476100.91</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>二阶</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="C3" t="n">
+        <v>358903.36</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>22.4%</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>152664</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>42.5%</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>206239.36</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>门店</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B4" t="n">
         <v>11300000</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C4" t="n">
         <v>2274653.87</v>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>20.1%</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E4" t="n">
         <v>271798.33</v>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>11.9%</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="G4" t="n">
         <v>2002855.54</v>
       </c>
     </row>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4300000</v>
       </c>
       <c r="C2" t="n">
-        <v>705390.7</v>
+        <v>761181.6699999999</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16.4%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229289.79</v>
+        <v>283442.79</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>476100.91</v>
+        <v>477738.8799999999</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1600000</v>
       </c>
       <c r="C3" t="n">
-        <v>358903.36</v>
+        <v>396147.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>152664</v>
+        <v>184916.88</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>206239.36</v>
+        <v>211230.48</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>11300000</v>
       </c>
       <c r="C4" t="n">
-        <v>2274653.87</v>
+        <v>2499065.24</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>271798.33</v>
+        <v>294993.33</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2002855.54</v>
+        <v>2204071.91</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4300000</v>
       </c>
       <c r="C2" t="n">
-        <v>761181.6699999999</v>
+        <v>868663.88</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>20.2%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>283442.79</v>
+        <v>314938.79</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>477738.8799999999</v>
+        <v>553725.0900000001</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1600000</v>
       </c>
       <c r="C3" t="n">
-        <v>396147.36</v>
+        <v>484621.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>184916.88</v>
+        <v>204996.88</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>211230.48</v>
+        <v>279624.48</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>11300000</v>
       </c>
       <c r="C4" t="n">
-        <v>2499065.24</v>
+        <v>2802005.9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>294993.33</v>
+        <v>348873.33</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2204071.91</v>
+        <v>2453132.57</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4300000</v>
       </c>
       <c r="C2" t="n">
-        <v>868663.88</v>
+        <v>1010577.88</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>314938.79</v>
+        <v>348196.79</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>553725.0900000001</v>
+        <v>662381.0900000001</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1600000</v>
       </c>
       <c r="C3" t="n">
-        <v>484621.36</v>
+        <v>623184.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>30.3%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>204996.88</v>
+        <v>235696.88</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>279624.48</v>
+        <v>387487.48</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>11300000</v>
       </c>
       <c r="C4" t="n">
-        <v>2802005.9</v>
+        <v>3010278.56</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>26.6%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>348873.33</v>
+        <v>367710.33</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2453132.57</v>
+        <v>2642568.23</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4300000</v>
       </c>
       <c r="C2" t="n">
-        <v>1010577.88</v>
+        <v>12082</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>348196.79</v>
+        <v>2085</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>662381.0900000001</v>
+        <v>9997</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1600000</v>
       </c>
       <c r="C3" t="n">
-        <v>623184.36</v>
+        <v>732</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>235696.88</v>
+        <v>299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>40.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>387487.48</v>
+        <v>433</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>11300000</v>
       </c>
       <c r="C4" t="n">
-        <v>3010278.56</v>
+        <v>867102.71</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>7.7%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>367710.33</v>
+        <v>1398.59</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2642568.23</v>
+        <v>865704.12</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -471,15 +471,15 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2085</v>
+        <v>349805.79</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>2895.3%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>9997</v>
+        <v>-337723.79</v>
       </c>
     </row>
     <row r="3">
@@ -500,15 +500,15 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>299</v>
+        <v>235995.88</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>40.8%</t>
+          <t>32239.9%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>433</v>
+        <v>-235263.88</v>
       </c>
     </row>
     <row r="4">
@@ -529,15 +529,15 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1398.59</v>
+        <v>369070.92</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>865704.12</v>
+        <v>498031.79</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,11 +463,11 @@
         <v>4300000</v>
       </c>
       <c r="C2" t="n">
-        <v>12082</v>
+        <v>1010872.88</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -475,11 +475,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2895.3%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>-337723.79</v>
+        <v>661067.0900000001</v>
       </c>
     </row>
     <row r="3">
@@ -492,11 +492,11 @@
         <v>1600000</v>
       </c>
       <c r="C3" t="n">
-        <v>732</v>
+        <v>623184.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -504,11 +504,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>32239.9%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-235263.88</v>
+        <v>387188.48</v>
       </c>
     </row>
     <row r="4">
@@ -521,11 +521,11 @@
         <v>11300000</v>
       </c>
       <c r="C4" t="n">
-        <v>867102.71</v>
+        <v>3024357.45</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7.7%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -533,11 +533,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>498031.79</v>
+        <v>2655286.53</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4300000</v>
       </c>
       <c r="C2" t="n">
-        <v>1010872.88</v>
+        <v>1269364.02</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>349805.79</v>
+        <v>356808.79</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>661067.0900000001</v>
+        <v>912555.23</v>
       </c>
     </row>
     <row r="3">
@@ -492,11 +492,11 @@
         <v>1600000</v>
       </c>
       <c r="C3" t="n">
-        <v>623184.36</v>
+        <v>1075132.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -504,11 +504,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>387188.48</v>
+        <v>839136.4799999999</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>11300000</v>
       </c>
       <c r="C4" t="n">
-        <v>3024357.45</v>
+        <v>3675771.99</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>369070.92</v>
+        <v>409115.92</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>2655286.53</v>
+        <v>3266656.07</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4300000</v>
       </c>
       <c r="C2" t="n">
-        <v>1269364.02</v>
+        <v>599949.4199999999</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>14.0%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>356808.79</v>
+        <v>374635.49</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>912555.23</v>
+        <v>225313.93</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1600000</v>
       </c>
       <c r="C3" t="n">
-        <v>1075132.36</v>
+        <v>799874</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>235995.88</v>
+        <v>262558.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>839136.4799999999</v>
+        <v>537315.46</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>11300000</v>
       </c>
       <c r="C4" t="n">
-        <v>3675771.99</v>
+        <v>2073431.55</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>409115.92</v>
+        <v>730094.92</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3266656.07</v>
+        <v>1343336.63</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4300000</v>
       </c>
       <c r="C2" t="n">
-        <v>599949.4199999999</v>
+        <v>1456865.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>374635.49</v>
+        <v>374702.49</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>225313.93</v>
+        <v>1082162.81</v>
       </c>
     </row>
     <row r="3">
@@ -492,11 +492,11 @@
         <v>1600000</v>
       </c>
       <c r="C3" t="n">
-        <v>799874</v>
+        <v>1291095.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -504,11 +504,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>537315.46</v>
+        <v>1028536.82</v>
       </c>
     </row>
     <row r="4">
@@ -521,11 +521,11 @@
         <v>11300000</v>
       </c>
       <c r="C4" t="n">
-        <v>2073431.55</v>
+        <v>4078011.38</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -533,11 +533,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1343336.63</v>
+        <v>3347916.46</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4300000</v>
       </c>
       <c r="C2" t="n">
-        <v>1456865.3</v>
+        <v>1471748.3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>374702.49</v>
+        <v>435086.49</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1082162.81</v>
+        <v>1036661.81</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1600000</v>
       </c>
       <c r="C3" t="n">
-        <v>1291095.36</v>
+        <v>1261983.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>262558.54</v>
+        <v>299119.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1028536.82</v>
+        <v>962863.8199999998</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>11300000</v>
       </c>
       <c r="C4" t="n">
-        <v>4078011.38</v>
+        <v>4117093.36</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>730094.92</v>
+        <v>798911.92</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3347916.46</v>
+        <v>3318181.44</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4300000</v>
       </c>
       <c r="C2" t="n">
-        <v>1471748.3</v>
+        <v>1682192.5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>435086.49</v>
+        <v>499719.39</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1036661.81</v>
+        <v>1182473.11</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1600000</v>
       </c>
       <c r="C3" t="n">
-        <v>1261983.36</v>
+        <v>1394627.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>299119.54</v>
+        <v>349147.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>962863.8199999998</v>
+        <v>1045479.82</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>11300000</v>
       </c>
       <c r="C4" t="n">
-        <v>4117093.36</v>
+        <v>6102698.76</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>798911.92</v>
+        <v>906758.92</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>14.9%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3318181.44</v>
+        <v>5195939.84</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,23 +463,23 @@
         <v>4300000</v>
       </c>
       <c r="C2" t="n">
-        <v>1682192.5</v>
+        <v>1674772.28</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>499719.39</v>
+        <v>499548.39</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1182473.11</v>
+        <v>1175223.89</v>
       </c>
     </row>
     <row r="3">
@@ -521,7 +521,7 @@
         <v>11300000</v>
       </c>
       <c r="C4" t="n">
-        <v>6102698.76</v>
+        <v>6097718.76</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -537,7 +537,36 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5195939.84</v>
+        <v>5190959.84</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>观澜组</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1300000</v>
+      </c>
+      <c r="C5" t="n">
+        <v>538346</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>41.4%</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>44760</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>8.3%</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>493586</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4300000</v>
       </c>
       <c r="C2" t="n">
-        <v>1674772.28</v>
+        <v>25847</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>499548.39</v>
+        <v>512872.39</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>1984.3%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1175223.89</v>
+        <v>-487025.39</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1600000</v>
       </c>
       <c r="C3" t="n">
-        <v>1394627.36</v>
+        <v>751</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>349147.54</v>
+        <v>359147.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>47822.6%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1045479.82</v>
+        <v>-358396.54</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>11300000</v>
       </c>
       <c r="C4" t="n">
-        <v>6097718.76</v>
+        <v>1323582.02</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>906758.92</v>
+        <v>965679.92</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5190959.84</v>
+        <v>357902.1000000002</v>
       </c>
     </row>
     <row r="5">
@@ -550,11 +550,11 @@
         <v>1300000</v>
       </c>
       <c r="C5" t="n">
-        <v>538346</v>
+        <v>2260</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -562,11 +562,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>1980.5%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>493586</v>
+        <v>-42500</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,11 +463,11 @@
         <v>4300000</v>
       </c>
       <c r="C2" t="n">
-        <v>25847</v>
+        <v>1933922.35</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -475,11 +475,11 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1984.3%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>-487025.39</v>
+        <v>1421049.96</v>
       </c>
     </row>
     <row r="3">
@@ -492,11 +492,11 @@
         <v>1600000</v>
       </c>
       <c r="C3" t="n">
-        <v>751</v>
+        <v>1446274.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -504,11 +504,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>47822.6%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>-358396.54</v>
+        <v>1087126.82</v>
       </c>
     </row>
     <row r="4">
@@ -521,11 +521,11 @@
         <v>11300000</v>
       </c>
       <c r="C4" t="n">
-        <v>1323582.02</v>
+        <v>6275328.59</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -533,11 +533,11 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>73.0%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>357902.1000000002</v>
+        <v>5309648.67</v>
       </c>
     </row>
     <row r="5">
@@ -550,11 +550,11 @@
         <v>1300000</v>
       </c>
       <c r="C5" t="n">
-        <v>2260</v>
+        <v>588664</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -562,11 +562,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1980.5%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>-42500</v>
+        <v>543904</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -424,12 +424,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>目标</t>
+          <t>目标(元)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>完成</t>
+          <t>完成(元)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -439,7 +439,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>本月退费</t>
+          <t>本月退费(元)</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -449,7 +449,7 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>本月净流水</t>
+          <t>本月净流水(元)</t>
         </is>
       </c>
     </row>
@@ -463,23 +463,23 @@
         <v>4300000</v>
       </c>
       <c r="C2" t="n">
-        <v>1933922.35</v>
+        <v>2186213.58</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>512872.39</v>
+        <v>552450.09</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1421049.96</v>
+        <v>1633763.49</v>
       </c>
     </row>
     <row r="3">
@@ -492,11 +492,11 @@
         <v>1600000</v>
       </c>
       <c r="C3" t="n">
-        <v>1446274.36</v>
+        <v>1506000.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -504,11 +504,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1087126.82</v>
+        <v>1146852.82</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>11300000</v>
       </c>
       <c r="C4" t="n">
-        <v>6275328.59</v>
+        <v>7462998.069999999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>965679.92</v>
+        <v>1036215.92</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>5309648.67</v>
+        <v>6426782.15</v>
       </c>
     </row>
     <row r="5">
@@ -550,11 +550,11 @@
         <v>1300000</v>
       </c>
       <c r="C5" t="n">
-        <v>588664</v>
+        <v>549614</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -562,11 +562,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>543904</v>
+        <v>504854</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4300000</v>
       </c>
       <c r="C2" t="n">
-        <v>2186213.58</v>
+        <v>2269503.58</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>552450.09</v>
+        <v>553042.09</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1633763.49</v>
+        <v>1716461.49</v>
       </c>
     </row>
     <row r="3">
@@ -492,11 +492,11 @@
         <v>1600000</v>
       </c>
       <c r="C3" t="n">
-        <v>1506000.36</v>
+        <v>1536337.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -504,11 +504,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1146852.82</v>
+        <v>1177189.82</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>11300000</v>
       </c>
       <c r="C4" t="n">
-        <v>7462998.069999999</v>
+        <v>8042459</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1036215.92</v>
+        <v>1036243.92</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>6426782.15</v>
+        <v>7006215.08</v>
       </c>
     </row>
     <row r="5">

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4300000</v>
       </c>
       <c r="C2" t="n">
-        <v>2269503.58</v>
+        <v>2525780.59</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>553042.09</v>
+        <v>594300.09</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1716461.49</v>
+        <v>1931480.5</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1600000</v>
       </c>
       <c r="C3" t="n">
-        <v>1536337.36</v>
+        <v>1558573.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>96.0%</t>
+          <t>97.4%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>359147.54</v>
+        <v>365747.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1177189.82</v>
+        <v>1192825.82</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>11300000</v>
       </c>
       <c r="C4" t="n">
-        <v>8042459</v>
+        <v>8443213.15</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>74.7%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1036243.92</v>
+        <v>1093402.92</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>7006215.08</v>
+        <v>7349810.23</v>
       </c>
     </row>
     <row r="5">

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4300000</v>
       </c>
       <c r="C2" t="n">
-        <v>2525780.59</v>
+        <v>2730565.58</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>594300.09</v>
+        <v>645956.09</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1931480.5</v>
+        <v>2084609.49</v>
       </c>
     </row>
     <row r="3">
@@ -492,11 +492,11 @@
         <v>1600000</v>
       </c>
       <c r="C3" t="n">
-        <v>1558573.36</v>
+        <v>1635045.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>97.4%</t>
+          <t>102.2%</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -504,11 +504,11 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1192825.82</v>
+        <v>1269297.82</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>11300000</v>
       </c>
       <c r="C4" t="n">
-        <v>8443213.15</v>
+        <v>8744441.439999999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>77.4%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1093402.92</v>
+        <v>1204339.92</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>7349810.23</v>
+        <v>7540101.52</v>
       </c>
     </row>
     <row r="5">
@@ -550,23 +550,23 @@
         <v>1300000</v>
       </c>
       <c r="C5" t="n">
-        <v>549614</v>
+        <v>692174</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44760</v>
+        <v>44940</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>8.1%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>504854</v>
+        <v>647234</v>
       </c>
     </row>
   </sheetData>

--- a/导出_按角色.xlsx
+++ b/导出_按角色.xlsx
@@ -463,23 +463,23 @@
         <v>4300000</v>
       </c>
       <c r="C2" t="n">
-        <v>2730565.58</v>
+        <v>3193290.16</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>645956.09</v>
+        <v>870071.09</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>27.2%</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2084609.49</v>
+        <v>2323219.07</v>
       </c>
     </row>
     <row r="3">
@@ -492,23 +492,23 @@
         <v>1600000</v>
       </c>
       <c r="C3" t="n">
-        <v>1635045.36</v>
+        <v>1893422.36</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>102.2%</t>
+          <t>118.3%</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>365747.54</v>
+        <v>449505.54</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1269297.82</v>
+        <v>1443916.82</v>
       </c>
     </row>
     <row r="4">
@@ -521,23 +521,23 @@
         <v>11300000</v>
       </c>
       <c r="C4" t="n">
-        <v>8744441.439999999</v>
+        <v>9627734.949999999</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>77.4%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204339.92</v>
+        <v>1405654.92</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>7540101.52</v>
+        <v>8222080.029999999</v>
       </c>
     </row>
     <row r="5">
@@ -550,23 +550,23 @@
         <v>1300000</v>
       </c>
       <c r="C5" t="n">
-        <v>692174</v>
+        <v>827354</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44940</v>
+        <v>46900</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>647234</v>
+        <v>780454</v>
       </c>
     </row>
   </sheetData>
